--- a/49891_Intercuenca_Alto_Maranon_I/_raw_reportes_xlsx/IDConfig_65372_completo.xlsx
+++ b/49891_Intercuenca_Alto_Maranon_I/_raw_reportes_xlsx/IDConfig_65372_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R175831f419c549fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R45246ffbe4cc40da"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,111 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.3200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.4256</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.4567</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6305</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.0420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6933</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49891_Intercuenca_Alto_Maranon_I/_raw_reportes_xlsx/IDConfig_65372_completo.xlsx
+++ b/49891_Intercuenca_Alto_Maranon_I/_raw_reportes_xlsx/IDConfig_65372_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R45246ffbe4cc40da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd59a4e52868e4659"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,351 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.4250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.4480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.5850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7108</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.7343</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2718</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.0550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9106</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.3417</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.3081</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.5517</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.3992</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.4488</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.5420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.5400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5182</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.3382</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.4927</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
